--- a/6주차_과제_최명원/05_대안비교_매트릭스.xlsx
+++ b/6주차_과제_최명원/05_대안비교_매트릭스.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pinky\OneDrive\Desktop\3학년 2학기\스마트도시계획\6주차_과제\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0588d38e3b12d3ea/Desktop/3학년 2학기/스마트도시계획/6주차_과제/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0FAB66-C45C-417B-BB9E-5D3CF2BF62CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_DBC862022759919B69134B27C997B03C0B477E47" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="186">
   <si>
     <t>6주차 과제 — 대안 비교 매트릭스 원본 (창신초 반경 400 m · 배분 대안 3안)</t>
   </si>
@@ -315,6 +315,12 @@
     <t>DEM</t>
   </si>
   <si>
+    <t>브이월드 레이어</t>
+  </si>
+  <si>
+    <t>경계 처리</t>
+  </si>
+  <si>
     <t>표본</t>
   </si>
   <si>
@@ -336,6 +342,12 @@
     <t>Copernicus GLO-90 90 m (Open-Meteo Elevation API) — 국토지리정보원 90 m 대용</t>
   </si>
   <si>
+    <t>LT_C_UQ111~114 용도지역(③과 중첩) · LP_PA_CBND_BUBUN 지목</t>
+  </si>
+  <si>
+    <t>표본 중심이 원(반경 400 m) 안이면 포함 — 중심점 규칙, 원 밖 이웃 표고는 경사 계산에만 사용</t>
+  </si>
+  <si>
     <t>격자 30 m · 561점 · 경사 차분 ±60 m</t>
   </si>
   <si>
@@ -384,7 +396,7 @@
     <t>급경사·재난위험지대 등 시가화 부적당지를 녹지로 먼저 묶는다</t>
   </si>
   <si>
-    <t>원본 13·14번 · 6주차 18쪽</t>
+    <t>원본 13·14번 · 국토계획법 제36조·시행령 제30조제1항제4호</t>
   </si>
   <si>
     <t>경사 25% 초과 면적(%)</t>
@@ -405,78 +417,84 @@
     <t>근린주구 생활권 안에서 일상적으로 걸어 이용할 수 있는 거리에 둔다</t>
   </si>
   <si>
-    <t>원본 13번 · 도시공원법 시행규칙 별표 3</t>
+    <t>원본 13번 · 도시공원법 제15조·시행규칙 별표 3</t>
+  </si>
+  <si>
+    <t>주거지 중 공원·녹지 500 m 이내(%)</t>
+  </si>
+  <si>
+    <t>근린생활권 근린공원 유치거리 500 m(별표 3) — 주거지의 80% 이상 충족 · 50~80% 조건부</t>
+  </si>
+  <si>
+    <t>주변환경</t>
+  </si>
+  <si>
+    <t>풍치·산림을 보전하고 위험시설과의 사이를 완충한다</t>
+  </si>
+  <si>
+    <t>원본 13·14번 · 도시공원법 제35조</t>
+  </si>
+  <si>
+    <t>임야 + 문화재보호구역(%)</t>
+  </si>
+  <si>
+    <t>조건부</t>
+  </si>
+  <si>
+    <t>보전할 산림·문화재 ≥5% 충족 · 0 초과 조건부</t>
+  </si>
+  <si>
+    <t>기반시설</t>
+  </si>
+  <si>
+    <t>녹지체계 위계(환상·방사·격자·분산)를 도시 전체와 잇는다</t>
+  </si>
+  <si>
+    <t>원본 13번</t>
+  </si>
+  <si>
+    <t>지표 없음(정성)</t>
+  </si>
+  <si>
+    <t>지표 없음</t>
+  </si>
+  <si>
+    <t>6주차 25쪽 — 측정 불가 낱말은 '지표 없음' 표기</t>
+  </si>
+  <si>
+    <t>유통·대형 시설은 경사 5% 이하 평지에 둔다</t>
+  </si>
+  <si>
+    <t>원본 17번 · 국토계획법 시행령 제30조제1항제2호</t>
+  </si>
+  <si>
+    <t>경사 5% 이하 면적(%)</t>
+  </si>
+  <si>
+    <t>≥50% 충족 · 20~50% 조건부</t>
+  </si>
+  <si>
+    <t>위계별 교통결절 — 중심은 교통망 집중지, 일반은 간선 교차점, 근린은 주거지 인접</t>
+  </si>
+  <si>
+    <t>원본 9·15~17번 · 6주차 14쪽</t>
+  </si>
+  <si>
+    <t>최근접 도시철도역(m)</t>
+  </si>
+  <si>
+    <t>역 500 m 이내 충족(역세권) · 1,000 m 이내 조건부</t>
+  </si>
+  <si>
+    <t>근린상업은 녹지와 이어 쾌적성을 유지한다</t>
+  </si>
+  <si>
+    <t>원본 17번</t>
   </si>
   <si>
     <t>공원·녹지 결정 면적(%)</t>
   </si>
   <si>
-    <t>도시공원법 시행규칙 별표 2 — 30만~100만㎡ 부지 9%(충족)·1만~30만㎡ 5%(조건부)</t>
-  </si>
-  <si>
-    <t>주변환경</t>
-  </si>
-  <si>
-    <t>풍치·산림을 보전하고 위험시설과의 사이를 완충한다</t>
-  </si>
-  <si>
-    <t>원본 13·14번 · 도시공원법 제35조</t>
-  </si>
-  <si>
-    <t>문화재보호구역(%)</t>
-  </si>
-  <si>
-    <t>&gt;0 이면 보전 대상 존재(충족)</t>
-  </si>
-  <si>
-    <t>기반시설</t>
-  </si>
-  <si>
-    <t>녹지체계 위계(환상·방사·격자·분산)를 도시 전체와 잇는다</t>
-  </si>
-  <si>
-    <t>원본 13번</t>
-  </si>
-  <si>
-    <t>지표 없음(정성)</t>
-  </si>
-  <si>
-    <t>지표 없음</t>
-  </si>
-  <si>
-    <t>6주차 25쪽 — 측정 불가 낱말은 '지표 없음' 표기</t>
-  </si>
-  <si>
-    <t>유통·대형 시설은 경사 5% 이하 평지에 둔다</t>
-  </si>
-  <si>
-    <t>원본 17번 · 6주차 16쪽</t>
-  </si>
-  <si>
-    <t>경사 5% 이하 면적(%)</t>
-  </si>
-  <si>
-    <t>≥50% 충족 · 20~50% 조건부</t>
-  </si>
-  <si>
-    <t>위계별 교통결절 — 중심은 교통망 집중지, 일반은 간선 교차점, 근린은 주거지 인접</t>
-  </si>
-  <si>
-    <t>원본 9·15~17번 · 6주차 14쪽</t>
-  </si>
-  <si>
-    <t>최근접 도시철도역(m)</t>
-  </si>
-  <si>
-    <t>역 500 m 이내 충족(역세권) · 1,000 m 이내 조건부</t>
-  </si>
-  <si>
-    <t>근린상업은 녹지와 이어 쾌적성을 유지한다</t>
-  </si>
-  <si>
-    <t>원본 17번</t>
-  </si>
-  <si>
     <t>≥5% 충족</t>
   </si>
   <si>
@@ -486,24 +504,21 @@
     <t>원본 16·17번</t>
   </si>
   <si>
-    <t>주거지역(%) — 배후 주거</t>
-  </si>
-  <si>
-    <t>≥40% 충족(근린 배후) · 10~40% 조건부</t>
+    <t>주거지역(%) — 배후인구 대용</t>
+  </si>
+  <si>
+    <t>인구(3~5만 명)는 SGIS 조회 대기 — 주거지역 ≥40% 면 조건부, 인구 확인 전엔 충족 판정 안 함</t>
   </si>
   <si>
     <t>경사 4~10%(바람직)·25% 한계, 표고는 기반시설 +50 m 이내</t>
   </si>
   <si>
-    <t>원본 19번 · 6주차 16·17쪽</t>
+    <t>원본 19번 · 국토계획법 시행령 제30조제1항제1호</t>
   </si>
   <si>
     <t>경사 10% 이하 면적(%)</t>
   </si>
   <si>
-    <t>조건부</t>
-  </si>
-  <si>
     <t>≥50% 충족 · 25~50% 조건부</t>
   </si>
   <si>
@@ -537,7 +552,7 @@
     <t>경사 5% 이하, 최소 규모 이상의 평탄지</t>
   </si>
   <si>
-    <t>원본 21번 · 6주차 19쪽</t>
+    <t>원본 21번 · 국토계획법 시행령 제30조제1항제3호</t>
   </si>
   <si>
     <t>화물수송·출퇴근 간선에 직결한다</t>
@@ -2256,7 +2271,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2271,7 +2286,7 @@
     <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="28" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>83</v>
       </c>
@@ -2302,13 +2317,19 @@
       <c r="J1" s="3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="28" x14ac:dyDescent="0.45">
+      <c r="K1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="112" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C2" s="8">
         <v>33.700000000000003</v>
@@ -2320,27 +2341,33 @@
         <v>8.19</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="112" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="28" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="B3" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C3" s="8">
         <v>48.1</v>
@@ -2352,27 +2379,33 @@
         <v>10.17</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="112" x14ac:dyDescent="0.45">
+      <c r="A4" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="28" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="B4" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C4" s="8">
         <v>75.400000000000006</v>
@@ -2384,27 +2417,33 @@
         <v>13.05</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G4" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="112" x14ac:dyDescent="0.45">
+      <c r="A5" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="28" x14ac:dyDescent="0.45">
-      <c r="A5" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="C5" s="8">
         <v>94.8</v>
@@ -2416,27 +2455,33 @@
         <v>14.13</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="28" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:12" ht="112" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C6" s="8">
         <v>100</v>
@@ -2448,27 +2493,33 @@
         <v>15.75</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G6" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="28" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="1:12" ht="112" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C7" s="8">
         <v>100</v>
@@ -2480,19 +2531,25 @@
         <v>15.75</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G7" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2523,31 +2580,31 @@
         <v>75</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2555,31 +2612,31 @@
         <v>78</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F2" s="15">
         <v>24.6</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H2" s="15">
         <v>0</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2587,31 +2644,31 @@
         <v>78</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F3" s="15">
+        <v>100</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F3" s="15">
-        <v>24.8</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="H3" s="15">
-        <v>9.6</v>
+        <v>100</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2619,31 +2676,31 @@
         <v>78</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F4" s="15">
-        <v>0.7</v>
+        <v>5.7</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H4" s="15">
         <v>0.4</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2651,59 +2708,59 @@
         <v>78</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F5" s="15"/>
       <c r="G5" s="4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="28" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
         <v>81</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F6" s="15">
         <v>15.2</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H6" s="15">
         <v>64.900000000000006</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2711,31 +2768,31 @@
         <v>81</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F7" s="15">
         <v>426</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H7" s="15">
         <v>291</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
@@ -2743,63 +2800,63 @@
         <v>81</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="F8" s="15">
         <v>24.8</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H8" s="15">
         <v>9.6</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="28" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
         <v>81</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F9" s="15">
         <v>90.6</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="H9" s="15">
         <v>3.7</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2807,31 +2864,31 @@
         <v>82</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F10" s="15">
         <v>33.700000000000003</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="H10" s="15">
         <v>94.8</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2839,31 +2896,31 @@
         <v>82</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F11" s="15">
         <v>426</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H11" s="15">
         <v>291</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2871,31 +2928,31 @@
         <v>82</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F12" s="15">
         <v>34.6</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H12" s="15">
         <v>31.2</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2903,63 +2960,63 @@
         <v>82</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>156</v>
-      </c>
       <c r="E13" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F13" s="15">
         <v>14.6</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="H13" s="15">
         <v>34.6</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="28" x14ac:dyDescent="0.45">
       <c r="A14" s="4" t="s">
         <v>80</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F14" s="15">
         <v>15.2</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H14" s="15">
         <v>64.900000000000006</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
@@ -2967,31 +3024,31 @@
         <v>80</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F15" s="15">
         <v>37.799999999999997</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H15" s="15">
         <v>65.099999999999994</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2999,31 +3056,31 @@
         <v>80</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -3031,27 +3088,27 @@
         <v>80</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H17" s="15"/>
       <c r="I17" s="4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/6주차_과제_최명원/05_대안비교_매트릭스.xlsx
+++ b/6주차_과제_최명원/05_대안비교_매트릭스.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0588d38e3b12d3ea/Desktop/3학년 2학기/스마트도시계획/6주차_과제/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pinky\OneDrive\Desktop\3학년 2학기\스마트도시계획\6주차_과제\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_DBC862022759919B69134B27C997B03C0B477E47" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135C9936-871B-4D33-9912-B32E93A99943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="187">
   <si>
     <t>6주차 과제 — 대안 비교 매트릭스 원본 (창신초 반경 400 m · 배분 대안 3안)</t>
   </si>
@@ -336,19 +336,19 @@
     <t>135~225° (북 0° 시계방향)</t>
   </si>
   <si>
-    <t>원 안 최저 22 m + 50 m 이내(가정)</t>
-  </si>
-  <si>
-    <t>Copernicus GLO-90 90 m (Open-Meteo Elevation API) — 국토지리정보원 90 m 대용</t>
+    <t>원 안 최저 셀 20 m + 50 m 이내(가정)</t>
+  </si>
+  <si>
+    <t>국토지리정보원 공개DEM 90 m (2025, 도엽 37608·37705, EPSG:5179)</t>
   </si>
   <si>
     <t>LT_C_UQ111~114 용도지역(③과 중첩) · LP_PA_CBND_BUBUN 지목</t>
   </si>
   <si>
-    <t>표본 중심이 원(반경 400 m) 안이면 포함 — 중심점 규칙, 원 밖 이웃 표고는 경사 계산에만 사용</t>
-  </si>
-  <si>
-    <t>격자 30 m · 561점 · 경사 차분 ±60 m</t>
+    <t>90 m 셀 중심이 원(반경 400 m) 안이면 포함 — 중심점 규칙, 도엽 가장자리 셀은 이웃이 없어 제외</t>
+  </si>
+  <si>
+    <t>90 m 셀 63개(셀 0.81 ha) · 경사·향 3×3 Horn</t>
   </si>
   <si>
     <t>2026-10-12</t>
@@ -363,7 +363,10 @@
     <t>종로구청</t>
   </si>
   <si>
-    <t>원 안 최저 25 m + 50 m 이내(가정)</t>
+    <t>원 안 최저 셀 29 m + 50 m 이내(가정)</t>
+  </si>
+  <si>
+    <t>90 m 셀 60개(셀 0.81 ha) · 경사·향 3×3 Horn</t>
   </si>
   <si>
     <t>축</t>
@@ -402,27 +405,30 @@
     <t>경사 25% 초과 면적(%)</t>
   </si>
   <si>
+    <t>조건부</t>
+  </si>
+  <si>
+    <t>미충족</t>
+  </si>
+  <si>
+    <t>≥10% 충족 · 0 초과 조건부(녹지 후보지 존재 여부)</t>
+  </si>
+  <si>
+    <t>접근성</t>
+  </si>
+  <si>
+    <t>근린주구 생활권 안에서 일상적으로 걸어 이용할 수 있는 거리에 둔다</t>
+  </si>
+  <si>
+    <t>원본 13번 · 도시공원법 제15조·시행규칙 별표 3</t>
+  </si>
+  <si>
+    <t>주거지 중 공원·녹지 500 m 이내(%)</t>
+  </si>
+  <si>
     <t>충족</t>
   </si>
   <si>
-    <t>미충족</t>
-  </si>
-  <si>
-    <t>≥10% 충족 · 0 초과 조건부(녹지 후보지 존재 여부)</t>
-  </si>
-  <si>
-    <t>접근성</t>
-  </si>
-  <si>
-    <t>근린주구 생활권 안에서 일상적으로 걸어 이용할 수 있는 거리에 둔다</t>
-  </si>
-  <si>
-    <t>원본 13번 · 도시공원법 제15조·시행규칙 별표 3</t>
-  </si>
-  <si>
-    <t>주거지 중 공원·녹지 500 m 이내(%)</t>
-  </si>
-  <si>
     <t>근린생활권 근린공원 유치거리 500 m(별표 3) — 주거지의 80% 이상 충족 · 50~80% 조건부</t>
   </si>
   <si>
@@ -436,9 +442,6 @@
   </si>
   <si>
     <t>임야 + 문화재보호구역(%)</t>
-  </si>
-  <si>
-    <t>조건부</t>
   </si>
   <si>
     <t>보전할 산림·문화재 ≥5% 충족 · 0 초과 조건부</t>
@@ -1343,13 +1346,13 @@
         <v>15</v>
       </c>
       <c r="B2" s="8">
-        <v>8.1999999999999993</v>
+        <v>7.3</v>
       </c>
       <c r="C2" s="8">
-        <v>36.700000000000003</v>
+        <v>31.5</v>
       </c>
       <c r="D2" s="8">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>54</v>
@@ -1386,7 +1389,7 @@
         <v>100</v>
       </c>
       <c r="C4" s="8">
-        <v>98.9</v>
+        <v>96.5</v>
       </c>
       <c r="D4" s="8">
         <v>100</v>
@@ -1406,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="8">
-        <v>46.2</v>
+        <v>44.4</v>
       </c>
       <c r="D5" s="8">
         <v>100</v>
@@ -1423,13 +1426,13 @@
         <v>38</v>
       </c>
       <c r="B6" s="8">
-        <v>64.400000000000006</v>
+        <v>58.9</v>
       </c>
       <c r="C6" s="8">
-        <v>48.4</v>
+        <v>44.4</v>
       </c>
       <c r="D6" s="8">
-        <v>64.099999999999994</v>
+        <v>58.6</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>54</v>
@@ -1443,13 +1446,13 @@
         <v>43</v>
       </c>
       <c r="B7" s="8">
-        <v>97.6</v>
+        <v>97.8</v>
       </c>
       <c r="C7" s="8">
-        <v>71.400000000000006</v>
+        <v>75.8</v>
       </c>
       <c r="D7" s="8">
-        <v>96.7</v>
+        <v>97.1</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>54</v>
@@ -1647,7 +1650,7 @@
       </c>
       <c r="C6" s="11">
         <f>IF(지표·가중치!E6="클수록 좋음",MIN(5,INT(지표값!B6/20)+1),MAX(1,5-INT(지표값!B6/20)))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" s="11">
         <f>IF(지표·가중치!E6="클수록 좋음",MIN(5,INT(지표값!C6/20)+1),MAX(1,5-INT(지표값!C6/20)))</f>
@@ -1655,11 +1658,11 @@
       </c>
       <c r="E6" s="11">
         <f>IF(지표·가중치!E6="클수록 좋음",MIN(5,INT(지표값!D6/20)+1),MAX(1,5-INT(지표값!D6/20)))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G6" s="7">
         <f t="shared" si="0"/>
@@ -1667,7 +1670,7 @@
       </c>
       <c r="H6" s="7">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
@@ -1710,7 +1713,7 @@
       </c>
       <c r="C8" s="7">
         <f>SUMPRODUCT($B$2:$B$7,C2:C7)</f>
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="D8" s="7">
         <f>SUMPRODUCT($B$2:$B$7,D2:D7)</f>
@@ -1718,7 +1721,7 @@
       </c>
       <c r="E8" s="7">
         <f>SUMPRODUCT($B$2:$B$7,E2:E7)</f>
-        <v>3.5999999999999996</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
@@ -1834,7 +1837,7 @@
       </c>
       <c r="E2" s="13">
         <f>(INDEX(채점·총점!$C$8:$E$8,MATCH(1,채점·총점!$C$9:$E$9,0))-B2*C2)/(1-B2)</f>
-        <v>4.7647058823529411</v>
+        <v>4.5294117647058822</v>
       </c>
       <c r="F2" s="13">
         <f>(INDEX(채점·총점!$C$8:$E$8,MATCH(2,채점·총점!$C$9:$E$9,0))-B2*D2)/(1-B2)</f>
@@ -1842,11 +1845,11 @@
       </c>
       <c r="G2" s="13">
         <f t="shared" ref="G2:G7" si="0">IF(ABS((C2-E2)-(D2-F2))&lt;0.000001,"",(F2-E2)/((C2-E2)-(D2-F2)))</f>
-        <v>0.45161290322580622</v>
+        <v>0.37037037037037007</v>
       </c>
       <c r="H2" s="4" t="str">
         <f t="shared" ref="H2:H7" si="1">IF(G2="","0~1 범위에서 1·2위 역전 없음",IF(AND(G2&gt;=0,G2&lt;0.999999),"가중치 "&amp;TEXT(G2,"0.000")&amp;IF(G2&gt;B2," 이상이면"," 이하이면")&amp;" 2위가 1위","0~1 범위에서 1·2위 역전 없음"))</f>
-        <v>가중치 0.452 이상이면 2위가 1위</v>
+        <v>가중치 0.370 이상이면 2위가 1위</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
@@ -1868,7 +1871,7 @@
       </c>
       <c r="E3" s="13">
         <f>(INDEX(채점·총점!$C$8:$E$8,MATCH(1,채점·총점!$C$9:$E$9,0))-B3*C3)/(1-B3)</f>
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="F3" s="13">
         <f>(INDEX(채점·총점!$C$8:$E$8,MATCH(2,채점·총점!$C$9:$E$9,0))-B3*D3)/(1-B3)</f>
@@ -1902,7 +1905,7 @@
       </c>
       <c r="E4" s="13">
         <f>(INDEX(채점·총점!$C$8:$E$8,MATCH(1,채점·총점!$C$9:$E$9,0))-B4*C4)/(1-B4)</f>
-        <v>4.1111111111111116</v>
+        <v>3.8888888888888888</v>
       </c>
       <c r="F4" s="13">
         <f>(INDEX(채점·총점!$C$8:$E$8,MATCH(2,채점·총점!$C$9:$E$9,0))-B4*D4)/(1-B4)</f>
@@ -1936,7 +1939,7 @@
       </c>
       <c r="E5" s="13">
         <f>(INDEX(채점·총점!$C$8:$E$8,MATCH(1,채점·총점!$C$9:$E$9,0))-B5*C5)/(1-B5)</f>
-        <v>4.0588235294117654</v>
+        <v>3.8235294117647061</v>
       </c>
       <c r="F5" s="13">
         <f>(INDEX(채점·총점!$C$8:$E$8,MATCH(2,채점·총점!$C$9:$E$9,0))-B5*D5)/(1-B5)</f>
@@ -1944,7 +1947,7 @@
       </c>
       <c r="G5" s="13">
         <f t="shared" si="0"/>
-        <v>-0.17241379310344848</v>
+        <v>-3.0303030303030193E-2</v>
       </c>
       <c r="H5" s="4" t="str">
         <f t="shared" si="1"/>
@@ -1962,7 +1965,7 @@
       </c>
       <c r="C6" s="11">
         <f>INDEX(채점·총점!$C6:$E6,MATCH(1,채점·총점!$C$9:$E$9,0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" s="11">
         <f>INDEX(채점·총점!$C6:$E6,MATCH(2,채점·총점!$C$9:$E$9,0))</f>
@@ -1978,7 +1981,7 @@
       </c>
       <c r="G6" s="13">
         <f t="shared" si="0"/>
-        <v>-0.77777777777777779</v>
+        <v>1</v>
       </c>
       <c r="H6" s="4" t="str">
         <f t="shared" si="1"/>
@@ -2004,7 +2007,7 @@
       </c>
       <c r="E7" s="13">
         <f>(INDEX(채점·총점!$C$8:$E$8,MATCH(1,채점·총점!$C$9:$E$9,0))-B7*C7)/(1-B7)</f>
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="F7" s="13">
         <f>(INDEX(채점·총점!$C$8:$E$8,MATCH(2,채점·총점!$C$9:$E$9,0))-B7*D7)/(1-B7)</f>
@@ -2012,7 +2015,7 @@
       </c>
       <c r="G7" s="13">
         <f t="shared" si="0"/>
-        <v>-0.77777777777777635</v>
+        <v>-0.23076923076923009</v>
       </c>
       <c r="H7" s="4" t="str">
         <f t="shared" si="1"/>
@@ -2061,10 +2064,10 @@
         <v>78</v>
       </c>
       <c r="C2" s="14">
-        <v>17.73</v>
+        <v>15.21</v>
       </c>
       <c r="D2" s="8">
-        <v>35.1</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
@@ -2117,10 +2120,10 @@
         <v>82</v>
       </c>
       <c r="C6" s="14">
-        <v>20.25</v>
+        <v>22.77</v>
       </c>
       <c r="D6" s="8">
-        <v>40.1</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
@@ -2131,10 +2134,10 @@
         <v>78</v>
       </c>
       <c r="C7" s="14">
-        <v>17.73</v>
+        <v>15.21</v>
       </c>
       <c r="D7" s="8">
-        <v>35.1</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
@@ -2159,10 +2162,10 @@
         <v>80</v>
       </c>
       <c r="C9" s="14">
-        <v>3.51</v>
+        <v>3.24</v>
       </c>
       <c r="D9" s="8">
-        <v>7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
@@ -2173,10 +2176,10 @@
         <v>81</v>
       </c>
       <c r="C10" s="14">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="D10" s="8">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
@@ -2187,10 +2190,10 @@
         <v>82</v>
       </c>
       <c r="C11" s="14">
-        <v>13.95</v>
+        <v>16.829999999999998</v>
       </c>
       <c r="D11" s="8">
-        <v>27.6</v>
+        <v>33.299999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
@@ -2201,10 +2204,10 @@
         <v>78</v>
       </c>
       <c r="C12" s="14">
-        <v>17.73</v>
+        <v>15.21</v>
       </c>
       <c r="D12" s="8">
-        <v>35.1</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
@@ -2257,10 +2260,10 @@
         <v>82</v>
       </c>
       <c r="C16" s="14">
-        <v>20.07</v>
+        <v>22.59</v>
       </c>
       <c r="D16" s="8">
-        <v>39.799999999999997</v>
+        <v>44.7</v>
       </c>
     </row>
   </sheetData>
@@ -2332,13 +2335,13 @@
         <v>96</v>
       </c>
       <c r="C2" s="8">
-        <v>33.700000000000003</v>
+        <v>34.9</v>
       </c>
       <c r="D2" s="8">
-        <v>16.2</v>
+        <v>20.6</v>
       </c>
       <c r="E2" s="8">
-        <v>8.19</v>
+        <v>10.53</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>97</v>
@@ -2370,13 +2373,13 @@
         <v>104</v>
       </c>
       <c r="C3" s="8">
-        <v>48.1</v>
+        <v>49.2</v>
       </c>
       <c r="D3" s="8">
-        <v>20.100000000000001</v>
+        <v>23.8</v>
       </c>
       <c r="E3" s="8">
-        <v>10.17</v>
+        <v>12.15</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>97</v>
@@ -2408,13 +2411,13 @@
         <v>105</v>
       </c>
       <c r="C4" s="8">
-        <v>75.400000000000006</v>
+        <v>90.5</v>
       </c>
       <c r="D4" s="8">
-        <v>25.8</v>
+        <v>30.2</v>
       </c>
       <c r="E4" s="8">
-        <v>13.05</v>
+        <v>15.39</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>97</v>
@@ -2446,13 +2449,13 @@
         <v>96</v>
       </c>
       <c r="C5" s="8">
-        <v>94.8</v>
+        <v>100</v>
       </c>
       <c r="D5" s="8">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="E5" s="8">
-        <v>14.13</v>
+        <v>29.16</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>97</v>
@@ -2470,7 +2473,7 @@
         <v>101</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>103</v>
@@ -2487,10 +2490,10 @@
         <v>100</v>
       </c>
       <c r="D6" s="8">
-        <v>31.2</v>
+        <v>60</v>
       </c>
       <c r="E6" s="8">
-        <v>15.75</v>
+        <v>29.16</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>97</v>
@@ -2508,7 +2511,7 @@
         <v>101</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>103</v>
@@ -2525,10 +2528,10 @@
         <v>100</v>
       </c>
       <c r="D7" s="8">
-        <v>31.2</v>
+        <v>60</v>
       </c>
       <c r="E7" s="8">
-        <v>15.75</v>
+        <v>29.16</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>97</v>
@@ -2546,7 +2549,7 @@
         <v>101</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>103</v>
@@ -2580,31 +2583,31 @@
         <v>75</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2612,31 +2615,31 @@
         <v>78</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F2" s="15">
-        <v>24.6</v>
+        <v>9.6</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H2" s="15">
         <v>0</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2644,31 +2647,31 @@
         <v>78</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F3" s="15">
         <v>100</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H3" s="15">
         <v>100</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2676,31 +2679,31 @@
         <v>78</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F4" s="15">
         <v>5.7</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H4" s="15">
         <v>0.4</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2708,27 +2711,27 @@
         <v>78</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F5" s="15"/>
       <c r="G5" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2736,31 +2739,31 @@
         <v>81</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F6" s="15">
-        <v>15.2</v>
+        <v>13.2</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H6" s="15">
-        <v>64.900000000000006</v>
+        <v>100</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2768,31 +2771,31 @@
         <v>81</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F7" s="15">
         <v>426</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H7" s="15">
         <v>291</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
@@ -2800,31 +2803,31 @@
         <v>81</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F8" s="15">
         <v>24.8</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H8" s="15">
         <v>9.6</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2832,31 +2835,31 @@
         <v>81</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F9" s="15">
         <v>90.6</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="H9" s="15">
         <v>3.7</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2864,31 +2867,31 @@
         <v>82</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F10" s="15">
-        <v>33.700000000000003</v>
+        <v>33.5</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="H10" s="15">
-        <v>94.8</v>
+        <v>100</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2896,31 +2899,31 @@
         <v>82</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F11" s="15">
         <v>426</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H11" s="15">
         <v>291</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2928,31 +2931,31 @@
         <v>82</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F12" s="15">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F12" s="15">
-        <v>34.6</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="H12" s="15">
-        <v>31.2</v>
+        <v>59.9</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2960,31 +2963,31 @@
         <v>82</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F13" s="15">
         <v>14.6</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="H13" s="15">
         <v>34.6</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -2992,31 +2995,31 @@
         <v>80</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F14" s="15">
-        <v>15.2</v>
+        <v>13.2</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H14" s="15">
-        <v>64.900000000000006</v>
+        <v>100</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
@@ -3024,31 +3027,31 @@
         <v>80</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F15" s="15">
         <v>37.799999999999997</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H15" s="15">
         <v>65.099999999999994</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -3056,31 +3059,31 @@
         <v>80</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="J16" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="28" x14ac:dyDescent="0.45">
@@ -3088,27 +3091,27 @@
         <v>80</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H17" s="15"/>
       <c r="I17" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
